--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -126,6 +131,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +596,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -603,7 +611,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -655,7 +663,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -692,7 +700,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -705,7 +713,7 @@
           <t>Mixed (Frontend + Backend)</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -744,7 +752,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -757,7 +765,7 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -796,7 +804,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -809,7 +817,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -848,7 +856,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -861,7 +869,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -913,7 +921,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -952,7 +960,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -965,7 +973,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1004,7 +1012,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1017,7 +1025,7 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1069,7 +1077,7 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1108,7 +1116,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1121,7 +1129,7 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1173,7 +1181,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1185,7 +1193,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1225,7 +1233,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1237,7 +1245,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1277,7 +1285,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1289,7 +1297,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1329,7 +1337,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1341,7 +1349,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1358,7 +1366,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 → LabResult persistence</t>
+          <t>ORU^R01 â†’ LabResult persistence</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1381,7 +1389,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1393,7 +1401,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1410,7 +1418,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ADT → Admission/Encounter sync</t>
+          <t>ADT â†’ Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1433,7 +1441,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1445,7 +1453,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1467,12 +1475,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1485,7 +1493,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1497,7 +1505,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1537,7 +1545,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1549,7 +1557,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1589,7 +1597,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1601,7 +1609,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1628,7 +1636,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1641,7 +1649,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1653,7 +1661,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1680,7 +1688,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1693,7 +1701,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1705,7 +1713,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1745,7 +1753,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1757,7 +1765,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1784,7 +1792,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1797,7 +1805,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1809,7 +1817,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1836,7 +1844,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1849,7 +1857,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1861,7 +1869,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1888,7 +1896,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1901,7 +1909,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1913,7 +1921,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1953,7 +1961,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1965,7 +1973,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1992,7 +2000,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2005,7 +2013,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2017,7 +2025,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2057,7 +2065,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2069,7 +2077,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2086,17 +2094,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>SOC 2 Type I → Type II</t>
+          <t>SOC 2 Type I â†’ Type II</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2109,7 +2117,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2121,7 +2129,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2143,12 +2151,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2161,7 +2169,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2173,7 +2181,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2195,12 +2203,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2213,7 +2221,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2225,7 +2233,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2265,7 +2273,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2277,7 +2285,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2304,7 +2312,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2317,7 +2325,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2329,7 +2337,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2356,7 +2364,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2369,7 +2377,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2381,7 +2389,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2421,7 +2429,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2433,7 +2441,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2473,7 +2481,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2485,14 +2493,14 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2507,44 +2515,44 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2559,44 +2567,44 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
+          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2611,44 +2619,44 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2663,44 +2671,44 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2715,32 +2723,32 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,7 +611,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>started</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>started</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -869,9 +877,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1193,7 +1201,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1245,7 +1253,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1297,7 +1305,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1349,7 +1357,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1401,7 +1409,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1453,7 +1461,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1505,7 +1513,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1557,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1609,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1661,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1713,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1765,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1817,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2493,7 +2501,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2533,7 +2541,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2545,7 +2553,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2585,7 +2593,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2597,7 +2605,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2637,7 +2645,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2649,7 +2657,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2689,7 +2697,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2741,7 +2749,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -973,9 +981,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1193,7 +1201,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1245,7 +1253,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1297,7 +1305,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1349,7 +1357,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1401,7 +1409,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1453,7 +1461,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1505,7 +1513,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1557,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1609,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1661,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1713,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1765,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1817,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2493,7 +2501,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2533,7 +2541,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2545,7 +2553,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2585,7 +2593,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2597,7 +2605,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2637,7 +2645,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2649,7 +2657,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2689,7 +2697,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2741,7 +2749,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1129,9 +1137,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1193,7 +1201,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1245,7 +1253,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1297,7 +1305,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1349,7 +1357,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1401,7 +1409,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1453,7 +1461,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1505,7 +1513,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1557,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1609,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1661,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1713,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1765,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1817,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2493,7 +2501,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2533,7 +2541,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2545,7 +2553,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2585,7 +2593,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2597,7 +2605,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2637,7 +2645,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2649,7 +2657,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2689,7 +2697,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2741,7 +2749,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -139,9 +134,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -877,9 +869,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -981,9 +973,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1137,9 +1129,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1253,7 +1245,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1305,7 +1297,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1357,7 +1349,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1409,7 +1401,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1461,7 +1453,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1513,7 +1505,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1565,7 +1557,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1617,7 +1609,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1669,7 +1661,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1721,7 +1713,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1773,7 +1765,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1825,7 +1817,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1877,7 +1869,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1929,7 +1921,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1981,7 +1973,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2033,7 +2025,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2085,7 +2077,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2137,7 +2129,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2189,7 +2181,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2241,7 +2233,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2293,7 +2285,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2345,7 +2337,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2397,7 +2389,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2449,7 +2441,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2501,7 +2493,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2541,7 +2533,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2553,7 +2545,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2593,7 +2585,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2605,7 +2597,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2645,7 +2637,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2657,7 +2649,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2697,7 +2689,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2709,7 +2701,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2749,7 +2741,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1025,9 +1033,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1193,7 +1201,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1245,7 +1253,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1297,7 +1305,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1349,7 +1357,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1401,7 +1409,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1453,7 +1461,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1505,7 +1513,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1557,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1609,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1661,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1713,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1765,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1817,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2493,7 +2501,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2533,7 +2541,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2545,7 +2553,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2585,7 +2593,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2597,7 +2605,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2637,7 +2645,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2649,7 +2657,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2689,7 +2697,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2741,7 +2749,7 @@
           <t>â€”</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>Mixed (Frontend + Backend)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -765,9 +765,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -817,9 +817,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -921,9 +921,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 â†’ LabResult persistence</t>
+          <t>ORU^R01 → LabResult persistence</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ADT â†’ Admission/Encounter sync</t>
+          <t>ADT → Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>SOC 2 Type I â†’ Type II</t>
+          <t>SOC 2 Type I → Type II</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
+          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2671,22 +2671,22 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -139,9 +134,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1033,9 +1025,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1085,7 +1077,7 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1189,7 +1181,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1201,7 +1193,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1241,7 +1233,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1253,7 +1245,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1293,7 +1285,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1305,7 +1297,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1345,7 +1337,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1357,7 +1349,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1397,7 +1389,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1409,7 +1401,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1449,7 +1441,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1461,7 +1453,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1501,7 +1493,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1513,7 +1505,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1553,7 +1545,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1565,7 +1557,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1605,7 +1597,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1617,7 +1609,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1657,7 +1649,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1669,7 +1661,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1709,7 +1701,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1721,7 +1713,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1761,7 +1753,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1773,7 +1765,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1813,7 +1805,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1825,7 +1817,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1865,7 +1857,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1877,7 +1869,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1917,7 +1909,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1929,7 +1921,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1969,7 +1961,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1981,7 +1973,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2021,7 +2013,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2033,7 +2025,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2073,7 +2065,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2085,7 +2077,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2125,7 +2117,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2137,7 +2129,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2177,7 +2169,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2189,7 +2181,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2229,7 +2221,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2241,7 +2233,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2281,7 +2273,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2293,7 +2285,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2333,7 +2325,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2345,7 +2337,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2385,7 +2377,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2397,7 +2389,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2437,7 +2429,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2449,7 +2441,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2489,7 +2481,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2501,7 +2493,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2541,7 +2533,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2553,7 +2545,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2593,7 +2585,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2605,7 +2597,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2645,7 +2637,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2657,7 +2649,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2697,7 +2689,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2709,7 +2701,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2749,7 +2741,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -596,7 +604,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -700,7 +708,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -752,7 +760,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -804,7 +812,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -856,7 +864,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -960,7 +968,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1012,7 +1020,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1079,7 +1087,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1116,7 +1124,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1181,7 +1189,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1193,7 +1201,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1233,7 +1241,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1245,7 +1253,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1285,7 +1293,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1297,7 +1305,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1337,7 +1345,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1349,7 +1357,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1366,7 +1374,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 → LabResult persistence</t>
+          <t>ORU^R01 â†’ LabResult persistence</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1389,7 +1397,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1401,7 +1409,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1418,7 +1426,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ADT → Admission/Encounter sync</t>
+          <t>ADT â†’ Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1441,7 +1449,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1453,7 +1461,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1475,12 +1483,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1493,7 +1501,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1505,7 +1513,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1545,7 +1553,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1557,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1597,7 +1605,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1609,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1636,7 +1644,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1649,7 +1657,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1661,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1688,7 +1696,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1701,7 +1709,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1713,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1753,7 +1761,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1765,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1792,7 +1800,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1805,7 +1813,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1817,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1844,7 +1852,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1857,7 +1865,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1896,7 +1904,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1909,7 +1917,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1961,7 +1969,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2000,7 +2008,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2013,7 +2021,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2065,7 +2073,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2094,17 +2102,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>SOC 2 Type I → Type II</t>
+          <t>SOC 2 Type I â†’ Type II</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2117,7 +2125,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2151,12 +2159,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2169,7 +2177,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2203,12 +2211,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2221,7 +2229,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2273,7 +2281,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2312,7 +2320,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2325,7 +2333,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2364,7 +2372,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2377,7 +2385,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2429,7 +2437,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2481,7 +2489,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2493,14 +2501,14 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2515,44 +2523,44 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2567,44 +2575,44 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
+          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2619,44 +2627,44 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2671,44 +2679,44 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2723,32 +2731,32 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -139,9 +134,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -604,7 +596,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -708,7 +700,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -760,7 +752,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -812,7 +804,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -864,7 +856,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -968,7 +960,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1085,9 +1077,9 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1124,7 +1116,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1189,7 +1181,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1201,7 +1193,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1241,7 +1233,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1253,7 +1245,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1293,7 +1285,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1305,7 +1297,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1345,7 +1337,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1357,7 +1349,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1374,7 +1366,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 â†’ LabResult persistence</t>
+          <t>ORU^R01 → LabResult persistence</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1397,7 +1389,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1409,7 +1401,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ADT â†’ Admission/Encounter sync</t>
+          <t>ADT → Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1449,7 +1441,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1461,7 +1453,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1483,12 +1475,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1501,7 +1493,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1513,7 +1505,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1553,7 +1545,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1565,7 +1557,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1605,7 +1597,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1617,7 +1609,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1644,7 +1636,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1657,7 +1649,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1669,7 +1661,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1696,7 +1688,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1709,7 +1701,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1721,7 +1713,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1761,7 +1753,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1773,7 +1765,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1800,7 +1792,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1813,7 +1805,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1825,7 +1817,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1852,7 +1844,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1865,7 +1857,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1877,7 +1869,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1904,7 +1896,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1917,7 +1909,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1929,7 +1921,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1969,7 +1961,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1981,7 +1973,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2008,7 +2000,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2021,7 +2013,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2033,7 +2025,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2073,7 +2065,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2085,7 +2077,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2102,17 +2094,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>SOC 2 Type I â†’ Type II</t>
+          <t>SOC 2 Type I → Type II</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2125,7 +2117,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2137,7 +2129,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2159,12 +2151,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2177,7 +2169,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2189,7 +2181,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2211,12 +2203,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2229,7 +2221,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2241,7 +2233,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2281,7 +2273,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2293,7 +2285,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2320,7 +2312,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2333,7 +2325,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2345,7 +2337,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2372,7 +2364,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2385,7 +2377,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2397,7 +2389,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2437,7 +2429,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2449,7 +2441,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2489,7 +2481,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2501,14 +2493,14 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2523,44 +2515,44 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2575,44 +2567,44 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
+          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2627,44 +2619,44 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2679,44 +2671,44 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2731,32 +2723,32 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>â€”</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,7 +1191,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1233,7 +1241,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1285,7 +1293,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1337,7 +1345,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1389,7 +1397,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1441,7 +1449,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1493,7 +1501,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1545,7 +1553,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1597,7 +1605,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1649,7 +1657,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1701,7 +1709,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1753,7 +1761,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1805,7 +1813,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1857,7 +1865,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1909,7 +1917,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1921,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1961,7 +1969,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1973,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2013,7 +2021,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2025,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2065,7 +2073,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2077,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2117,7 +2125,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2129,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2169,7 +2177,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2181,7 +2189,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2221,7 +2229,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2233,7 +2241,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2273,7 +2281,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2285,7 +2293,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2325,7 +2333,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2337,7 +2345,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2377,7 +2385,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2389,7 +2397,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2429,7 +2437,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2441,7 +2449,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2481,7 +2489,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2493,7 +2501,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2533,7 +2541,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2545,7 +2553,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2585,7 +2593,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2597,7 +2605,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2637,7 +2645,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2649,7 +2657,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2689,7 +2697,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2741,7 +2749,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Tag, signed release notes from CHANGELOG.md, freeze feat/* for 1 week, only fix/* allowed during soak</t>
+          <t>Tag, signed release notes from CHANGELOG.md, pre-pilot soak (one overnight CI run + one DR rehearsal, ~24-36h); 7-day feat/* freeze + fix/*-only policy kicks in for v1.1.0 onward (first pilot deploy)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -139,9 +134,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1189,9 +1181,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>started</t>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1241,7 +1233,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1253,7 +1245,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1293,7 +1285,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1305,7 +1297,7 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1345,7 +1337,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1357,7 +1349,7 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1397,7 +1389,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1409,7 +1401,7 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1449,7 +1441,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1461,7 +1453,7 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1501,7 +1493,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1513,7 +1505,7 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1553,7 +1545,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1565,7 +1557,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1605,7 +1597,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1617,7 +1609,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1657,7 +1649,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1669,7 +1661,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1709,7 +1701,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1721,7 +1713,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1761,7 +1753,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1773,7 +1765,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1813,7 +1805,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1825,7 +1817,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1865,7 +1857,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1877,7 +1869,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1917,7 +1909,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1929,7 +1921,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -1969,7 +1961,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1981,7 +1973,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2021,7 +2013,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2033,7 +2025,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2073,7 +2065,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2085,7 +2077,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2125,7 +2117,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2137,7 +2129,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2177,7 +2169,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2189,7 +2181,7 @@
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2229,7 +2221,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2241,7 +2233,7 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2281,7 +2273,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2293,7 +2285,7 @@
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2333,7 +2325,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2345,7 +2337,7 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2385,7 +2377,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2397,7 +2389,7 @@
       </c>
     </row>
     <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2437,7 +2429,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2449,7 +2441,7 @@
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
         </is>
@@ -2489,7 +2481,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2501,7 +2493,7 @@
       </c>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2541,7 +2533,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2553,7 +2545,7 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2593,7 +2585,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
@@ -2605,7 +2597,7 @@
       </c>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2645,7 +2637,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2657,7 +2649,7 @@
       </c>
     </row>
     <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2697,7 +2689,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
@@ -2709,7 +2701,7 @@
       </c>
     </row>
     <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
@@ -2749,7 +2741,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Roadmap" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roadmap'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roadmap'!$A$1:$J$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Roadmap'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -135,6 +135,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -923,7 +926,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>not-started</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1193,314 +1196,314 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Interop FHIR</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>FHIR write API</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>FHIR read API (done)</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Keycloak env-sync audit + remediation runbooks</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Audit doc + 4 runbooks under docs/runbooks/ (env-sync-audit-2026-05-12.md, realm-sync.md, railway-env-matrix.md, env-sync-remediation.md). Documents 6 drift surfaces, partial-import discipline, per-env Railway variable contract, snapshot-redaction policy. Per-env OIDC_REQUIRED intent table added to docs/keycloak-implementation-gaps.md.</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Keycloak env-sync verify script</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>scripts/keycloak/env-sync-verify.sh with --public-only (default) and --full modes. Repo-wide checks R1-R4 (branch divergence, redirect-URI coverage, frontend env-file consistency) + per-env public P1-P4 (OIDC discovery, issuer match, HTTPS, frontend agreement) + authenticated A1-A3 (live realm clients diff, role count, dev.* policy compliance).</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Keycloak env-sync audit + remediation runbooks</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>dev.* user policy + machine enforcement</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>keycloak/README.md per-env policy table: dev.admin forbidden on all hosted environments (super-admin via repo-published password); dev.doctor + dev.patient allowed on hosted dev only as test fixtures. Machine-enforced via env-sync-verify.sh A3 check.</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Keycloak env-sync audit + remediation runbooks</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>KC-4 user migration to hosted dev</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>21 HMS DB users migrated into hms-keycloak-dev hms realm via scripts/keycloak-migration. Gmail SMTP integration live (App Password + auth + StartTLS port 587). End-to-end verified: real user received and clicked setup email. 2 example.com test users (nurse_a, nurse_c) + dev.admin cleaned up via Admin REST. Realm clients partial-imported to align with realm-export.json (redirect URIs, web origins).</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Keycloak env-sync audit + remediation runbooks</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>KC-4 user migration to uat</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak ≥ 5 business days before promoting to prod.</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>KC-4 user migration to hosted dev</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Interop FHIR</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>FHIR Bulk Data Access ($export)</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Bulk export for Patient and Group; output to S3-compatible bucket; documented in docs/fhir-bulk.md</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>FHIR write API</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>KC-4 user migration to prod</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Apply same playbook to hms-keycloak-prod during announced maintenance window per docs/runbooks/keycloak-cutover-runbook.md. Prereq: uat soak clean. Pairs with the existing 'Keycloak Phase C cutover' row (which covers the OIDC_REQUIRED=true flip that gates legacy auth).</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>KC-4 user migration to uat</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Interop FHIR</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>FHIR $everything operation</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Patient compartment export; required by most HIE handshakes</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>FHIR write API</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Interop HL7</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>ORU^R01 → LabResult persistence</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Match by accession number; write to existing lab_result schema; link to encounter; integration tested with Mindray/Sysmex sample messages</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>HL7 MLLP listener (done)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Interop HL7</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>ADT → Admission/Encounter sync</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>HL7 MLLP listener (done)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Patient Identity</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>EMPI v0 (intra-tenant)</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Frontend)</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>#h1.exit</t>
         </is>
       </c>
     </row>
@@ -1517,27 +1520,27 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Clinical Safety</t>
+          <t>Interop FHIR</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>CDS Hooks LOINC binding</t>
+          <t>FHIR write API</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD</t>
+          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>CDS Hooks expansion (v1.0)</t>
+          <t>FHIR read API (done)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1569,27 +1572,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Clinical Safety</t>
+          <t>Interop FHIR</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>CDS Hooks public discovery</t>
+          <t>FHIR Bulk Data Access ($export)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox</t>
+          <t>Bulk export for Patient and Group; output to S3-compatible bucket; documented in docs/fhir-bulk.md</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CDS Hooks expansion (v1.0)</t>
+          <t>FHIR write API</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1621,32 +1624,32 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Interop FHIR</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Patient mobile parity (Android)</t>
+          <t>FHIR $everything operation</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability</t>
+          <t>Patient compartment export; required by most HIE handshakes</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FHIR write API</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1673,32 +1676,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Interop HL7</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Patient mobile parity (iOS)</t>
+          <t>ORU^R01 → LabResult persistence</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability</t>
+          <t>Match by accession number; write to existing lab_result schema; link to encounter; integration tested with Mindray/Sysmex sample messages</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HL7 MLLP listener (done)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1725,22 +1728,22 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Interop HL7</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Push notifications for lab results</t>
+          <t>ADT → Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail</t>
+          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Mobile parity</t>
+          <t>HL7 MLLP listener (done)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1750,7 +1753,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Mixed (Mobile + Backend)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1777,17 +1780,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Patient Identity</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Mobile test coverage uplift</t>
+          <t>EMPI v0 (intra-tenant)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1797,12 +1800,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1829,354 +1832,354 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>Clinical Safety</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks LOINC binding</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks expansion (v1.0)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Safety</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks public discovery</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks expansion (v1.0)</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Patient mobile parity (Android)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Patient mobile parity (iOS)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Push notifications for lab results</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Mobile parity</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Mobile + Backend)</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile test coverage uplift</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>KPI dashboard service</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Multi-tenancy</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Schema-per-tenant migration path</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign)</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Platform)</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Multi-tenancy</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Tenant onboarding pipeline</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Schema-per-tenant migration path</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Read replicas + Hikari tuning</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Async dispense + lab via Kafka</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>ORU^R01 persistence</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SOC 2 Type I → Type II</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Compliance + Backend)</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>HIPAA-equivalent posture</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2196,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Multi-tenancy</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>ECOWAS data-residency support</t>
+          <t>Schema-per-tenant migration path</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
+          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2213,12 +2216,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2245,22 +2248,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Patient Identity</t>
+          <t>Multi-tenancy</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>EMPI v1 (cross-tenant)</t>
+          <t>Tenant onboarding pipeline</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent</t>
+          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>EMPI v0</t>
+          <t>Schema-per-tenant migration path</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2270,7 +2273,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -2297,17 +2300,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Clinical Depth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>OB/GYN + pediatrics finish</t>
+          <t>Read replicas + Hikari tuning</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI</t>
+          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2317,12 +2320,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Mixed (Backend + Frontend)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -2349,22 +2352,22 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Clinical Depth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>DICOM proxy</t>
+          <t>Async dispense + lab via Kafka</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing</t>
+          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ORU^R01 persistence</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2374,7 +2377,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Mixed (Backend + Frontend)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -2401,32 +2404,32 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Synthetic monitoring</t>
+          <t>SOC 2 Type I → Type II</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DR runbook</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -2453,307 +2456,619 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>HIPAA-equivalent posture</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>ECOWAS data-residency support</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Patient Identity</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>EMPI v1 (cross-tenant)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>EMPI v0</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Depth</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>OB/GYN + pediatrics finish</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Frontend)</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Depth</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>DICOM proxy</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Frontend)</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic monitoring</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>DR runbook</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Per-tenant cost observability</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Tag every Splunk event + Grafana series with tenant; chargeback report per hospital</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Splunk HEC (done #276)</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>#h3.exit</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>AI/LLM clinical features</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Splunk Observability Cloud (metrics)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Jenkins</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Direct LDAP/Kerberos in hospital-core</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Revenue-cycle / claims module</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -57,17 +57,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,8 +141,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,7 +604,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -703,7 +708,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -807,7 +812,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -859,7 +864,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -924,7 +929,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -963,7 +968,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1015,7 +1020,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1196,319 +1201,319 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Audit doc + 4 runbooks under docs/runbooks/ (env-sync-audit-2026-05-12.md, realm-sync.md, railway-env-matrix.md, env-sync-remediation.md). Documents 6 drift surfaces, partial-import discipline, per-env Railway variable contract, snapshot-redaction policy. Per-env OIDC_REQUIRED intent table added to docs/keycloak-implementation-gaps.md.</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync verify script</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>scripts/keycloak/env-sync-verify.sh with --public-only (default) and --full modes. Repo-wide checks R1-R4 (branch divergence, redirect-URI coverage, frontend env-file consistency) + per-env public P1-P4 (OIDC discovery, issuer match, HTTPS, frontend agreement) + authenticated A1-A3 (live realm clients diff, role count, dev.* policy compliance).</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>dev.* user policy + machine enforcement</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>keycloak/README.md per-env policy table: dev.admin forbidden on all hosted environments (super-admin via repo-published password); dev.doctor + dev.patient allowed on hosted dev only as test fixtures. Machine-enforced via env-sync-verify.sh A3 check.</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to hosted dev</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>21 HMS DB users migrated into hms-keycloak-dev hms realm via scripts/keycloak-migration. Gmail SMTP integration live (App Password + auth + StartTLS port 587). End-to-end verified: real user received and clicked setup email. 2 example.com test users (nurse_a, nurse_c) + dev.admin cleaned up via Admin REST. Realm clients partial-imported to align with realm-export.json (redirect URIs, web origins).</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to uat</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak ≥ 5 business days before promoting to prod.</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak â‰¥ 5 business days before promoting to prod.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to hosted dev</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to prod</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Apply same playbook to hms-keycloak-prod during announced maintenance window per docs/runbooks/keycloak-cutover-runbook.md. Prereq: uat soak clean. Pairs with the existing 'Keycloak Phase C cutover' row (which covers the OIDC_REQUIRED=true flip that gates legacy auth).</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to uat</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1548,7 +1553,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1560,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1600,7 +1605,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1612,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1652,7 +1657,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1664,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 → LabResult persistence</t>
+          <t>ORU^R01 â†’ LabResult persistence</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1704,7 +1709,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1716,7 +1721,7 @@
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1733,7 +1738,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ADT → Admission/Encounter sync</t>
+          <t>ADT â†’ Admission/Encounter sync</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1756,7 +1761,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1768,7 +1773,7 @@
       </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1790,12 +1795,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1808,7 +1813,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1820,7 +1825,7 @@
       </c>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1860,7 +1865,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1872,7 +1877,7 @@
       </c>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1912,7 +1917,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1924,7 +1929,7 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1951,7 +1956,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1964,7 +1969,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1976,7 +1981,7 @@
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2016,7 +2021,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2028,7 +2033,7 @@
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -2068,7 +2073,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2080,7 +2085,7 @@
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -2107,7 +2112,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2120,7 +2125,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2132,7 +2137,7 @@
       </c>
     </row>
     <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2172,7 +2177,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2211,7 +2216,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2224,7 +2229,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2276,7 +2281,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2315,7 +2320,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2328,7 +2333,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2380,7 +2385,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2409,17 +2414,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>SOC 2 Type I → Type II</t>
+          <t>SOC 2 Type I â†’ Type II</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window. Foundation pass landed on feat/v2.0-soc2-gap-analysis: docs/compliance/soc2-gap.md (full control inventory across CC1-CC9 + Availability + Confidentiality, scorecard 12 present / 19 partial / 7 gap of 38 control points; CC6/CC7/CC8 axis at 71% weighted), companion machine-readable docs/compliance/soc2-controls.csv (38 rows with owner/priority/effort/target_close), and 24-item prioritised remediation backlog (10 P0 / 7 P1 / 7 P2) with critical path: P0 closes by 2026-08-15 -&gt; Type I fieldwork 2026-11 -&gt; observation window 2026-11..2027-11 -&gt; Type II report early 2028.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2432,9 +2437,9 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2466,12 +2471,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2484,7 +2489,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2518,12 +2523,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2536,7 +2541,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2588,7 +2593,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2640,7 +2645,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2679,7 +2684,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2692,7 +2697,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2744,7 +2749,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="38" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>v2.0</t>
@@ -2796,7 +2801,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2807,15 +2812,15 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="45" ht="38" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2830,44 +2835,44 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2882,44 +2887,44 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
+          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2934,44 +2939,44 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="38" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2986,44 +2991,44 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3038,32 +3043,32 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -33,7 +33,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,8 +141,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,7 +604,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -703,7 +708,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -807,7 +812,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -859,7 +864,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -924,7 +929,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -963,7 +968,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1015,7 +1020,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1196,319 +1201,319 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Audit doc + 4 runbooks under docs/runbooks/ (env-sync-audit-2026-05-12.md, realm-sync.md, railway-env-matrix.md, env-sync-remediation.md). Documents 6 drift surfaces, partial-import discipline, per-env Railway variable contract, snapshot-redaction policy. Per-env OIDC_REQUIRED intent table added to docs/keycloak-implementation-gaps.md.</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync verify script</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>scripts/keycloak/env-sync-verify.sh with --public-only (default) and --full modes. Repo-wide checks R1-R4 (branch divergence, redirect-URI coverage, frontend env-file consistency) + per-env public P1-P4 (OIDC discovery, issuer match, HTTPS, frontend agreement) + authenticated A1-A3 (live realm clients diff, role count, dev.* policy compliance).</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>dev.* user policy + machine enforcement</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>keycloak/README.md per-env policy table: dev.admin forbidden on all hosted environments (super-admin via repo-published password); dev.doctor + dev.patient allowed on hosted dev only as test fixtures. Machine-enforced via env-sync-verify.sh A3 check.</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to hosted dev</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>21 HMS DB users migrated into hms-keycloak-dev hms realm via scripts/keycloak-migration. Gmail SMTP integration live (App Password + auth + StartTLS port 587). End-to-end verified: real user received and clicked setup email. 2 example.com test users (nurse_a, nurse_c) + dev.admin cleaned up via Admin REST. Realm clients partial-imported to align with realm-export.json (redirect URIs, web origins).</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Keycloak env-sync audit + remediation runbooks</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to uat</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak ≥ 5 business days before promoting to prod.</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak â‰¥ 5 business days before promoting to prod.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to hosted dev</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to prod</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Apply same playbook to hms-keycloak-prod during announced maintenance window per docs/runbooks/keycloak-cutover-runbook.md. Prereq: uat soak clean. Pairs with the existing 'Keycloak Phase C cutover' row (which covers the OIDC_REQUIRED=true flip that gates legacy auth).</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>KC-4 user migration to uat</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>#h1.exit</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1548,7 +1553,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1560,7 +1565,7 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1600,7 +1605,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1612,7 +1617,7 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1652,7 +1657,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1664,7 +1669,7 @@
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
@@ -1681,12 +1686,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ORU^R01 → LabResult persistence</t>
+          <t>ORU^R01 â†’ LabResult persistence</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Match by accession number; write to existing lab_result schema; link to encounter; integration tested with Mindray/Sysmex sample messages</t>
+          <t>Match by accession number; write to existing lab_result schema; link to encounter; integration tested with Mindray/Sysmex sample messages. Shipped on feat/v1.1-oru-r01-lab-persistence: MllpInboundLabServiceImpl already had core ingestion (LabSpecimen.accessionNumber match -&gt; LabOrder -&gt; Encounter, SYSTEM-actor LabResult write, cross-tenant guard); added (1) MSH-10 idempotency via V98 + LabResult.sourceMessageControlId + partial unique index (analyzer retransmits collapse), (2) IntegrationMessageRecorder wiring for replay/DLQ surface, (3) AuditEventType.LAB_RESULT_UPDATED emission on every accepted ingest, (4) OruR01VendorSampleIngestionTest with realistic Mindray BS-240 (LOINC) + Sysmex XN-1000 (CBC panel, LL critical flag) sample messages plus a retransmit-delegation test.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1704,1118 +1709,1118 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Interop HL7</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>ADT â†’ Admission/Encounter sync</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>HL7 MLLP listener (done)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>#h2.exit</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Interop HL7</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ADT → Admission/Encounter sync</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>HL7 MLLP listener (done)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Patient Identity</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>EMPI v0 (intra-tenant)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Frontend)</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Safety</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks LOINC binding</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks expansion (v1.0)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Safety</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks public discovery</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>CDS Hooks expansion (v1.0)</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Patient mobile parity (Android)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Patient mobile parity (iOS)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Push notifications for lab results</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Mobile parity</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Mobile + Backend)</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile test coverage uplift</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>KPI dashboard service</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Frontend)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>#h2.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Schema-per-tenant migration path</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign)</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Platform)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Tenant onboarding pipeline</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Schema-per-tenant migration path</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Read replicas + Hikari tuning</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="38" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Async dispense + lab via Kafka</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>ORU^R01 persistence</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>SOC 2 Type I â†’ Type II</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1â€“CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Compliance + Backend)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>HIPAA-equivalent posture</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>ECOWAS data-residency support</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Patient Identity</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>EMPI v0 (intra-tenant)</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; ≥90% recall on labelled audit set</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>EMPI v1 (cross-tenant)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>EMPI v0</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Depth</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>OB/GYN + pediatrics finish</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Clinical Safety</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>CDS Hooks LOINC binding</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>CDS Hooks expansion (v1.0)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Clinical Depth</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>DICOM proxy</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Mixed (Backend + Frontend)</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>not-started</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic monitoring</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>DR runbook</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Clinical Safety</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>CDS Hooks public discovery</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>CDS Hooks expansion (v1.0)</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>#h3.exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Per-tenant cost observability</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Tag every Splunk event + Grafana series with tenant; chargeback report per hospital</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Splunk HEC (done #276)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Patient mobile parity (Android)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Patient mobile parity (iOS)</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Push notifications for lab results</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Mobile parity</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Mobile + Backend)</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Mobile test coverage uplift</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>v1.1</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Reporting</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>KPI dashboard service</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Frontend)</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>#h2.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Multi-tenancy</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Schema-per-tenant migration path</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign)</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Platform)</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>#h3.exit</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Multi-tenancy</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Tenant onboarding pipeline</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Schema-per-tenant migration path</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Read replicas + Hikari tuning</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Async dispense + lab via Kafka</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>ORU^R01 persistence</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>SOC 2 Type I → Type II</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Control map (existing audit logs/RBAC/encryption cover ~60% of CC1–CC9); gap analysis in docs/compliance/soc2-gap.md; 12-month observation window</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Compliance + Backend)</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>HIPAA-equivalent posture</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence — for international customers</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>ECOWAS data-residency support</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Per-tenant region pinning (Railway → AWS or OVH-Africa); required for Senegal/Côte d'Ivoire/Ghana sales</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Patient Identity</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>EMPI v1 (cross-tenant)</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>EMPI v0</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Clinical Depth</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>OB/GYN + pediatrics finish</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Frontend)</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Clinical Depth</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>DICOM proxy</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Mixed (Backend + Frontend)</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Synthetic monitoring</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>DR runbook</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Per-tenant cost observability</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Tag every Splunk event + Grafana series with tenant; chargeback report per hospital</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Splunk HEC (done #276)</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>not-started</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>#h3.exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="45" ht="38" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2830,44 +2835,44 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Deferred — regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
+          <t>Deferred â€” regulatorily risky in healthcare; no existing groundwork in repo. Revisit after v1.0</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2882,44 +2887,44 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Deferred — duplicates the OTel→Grafana Cloud path landed in #276</t>
+          <t>Deferred â€” duplicates the OTelâ†’Grafana Cloud path landed in #276</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2934,44 +2939,44 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Dropped — GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
+          <t>Dropped â€” GitHub Actions already covers CI/CD; Jenkins would be parallel duplication</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="38" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2986,44 +2991,44 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Dropped — auth concerns belong in Keycloak; configure user federation there per deployment</t>
+          <t>Dropped â€” auth concerns belong in Keycloak; configure user federation there per deployment</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>dropped</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>oos</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3038,32 +3043,32 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Deferred — out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
+          <t>Deferred â€” out of scope for clinical+pharmacy MVP; partner with a billing vendor instead</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
+          <t>â€”</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>deferred</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2211,7 +2211,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign)</t>
+          <t>Row-level multi-tenancy stays default; schema-per-tenant available for hospitals with strong isolation needs (military, private foreign). Foundation pass landed on feat/v2.0-schema-per-tenant: TenantIsolationMode enum, Hospital.isolationMode + tenantSchemaName columns (V97 + CHECK constraints + partial unique index), SchemaTenantIdentifierResolver + SchemaTenantConnectionProvider + TenantSchemaLookup behind app.tenancy.schema-isolation.enabled (off by default), 28 unit tests, operational runbook docs/runbooks/schema-per-tenant-migration.md. Follow-on PRs: provision-schema.sh, copy-rows.sh, cache-invalidate endpoint.</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2229,9 +2229,9 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented</t>
+          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented. Foundation pass shipped on feat/v1.1-adt-admission-encounter-sync (PR #332): V99 migration adds external_visit_number + external_sending_application + external_sending_facility + external_message_control_id (nullable) to admissions and clinical.encounters with partial composite unique indexes scoped per (sender, hospital); MllpInboundAdtVisitProjectionService reconciles inbound A01/A04/A08 against existing rows by the HL7 visit-number triplet, REQUIRES_NEW so projection failure cannot roll back the demographic write; gated behind app.hl7.adt.visit-sync.enabled (default false) so flag-off behaviour is bit-for-bit unchanged. Conflict-resolution rules + operator playbook in docs/runbooks/hl7-adt-conflict-resolution.md. Auto-create deferred to a follow-on PR (needs per-hospital intake-provider config).</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1761,9 +1761,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD</t>
+          <t>Bind hms-patient-view problem cards to LOINC alongside existing ICD. Shipped on feat/v1.1-cds-hooks-loinc-binding (PR #333): V100 migration adds loinc_code + loinc_display (nullable) to clinical.patient_problems; ProblemLoincBindings seed table (13 entries spanning cardio / endocrine / respiratory / hematology / malaria / HIV / TB / renal / OB â€” chosen for the WHO-EMRO chronic-care workload pilot hospitals see); PatientViewCdsService.renderProblem now appends typed [ICD-10: ...] and [LOINC: ...] annotations to each problem line, with entity-explicit loincCode taking precedence over the seed fallback. Malformed codes (failing TerminologyCodes regex) are dropped silently â€” card still renders, just without the annotation. 10 new tests cover prefix resolution, subdivision tolerance, case/whitespace, unknown codes, malformed input, and a defence-in-depth check that every seeded LOINC passes the global LOINC regex.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1865,9 +1865,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards</t>
+          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards. Foundation pass shipped on feat/v2.0-read-replicas-hikari (PR #334): full Hikari tuning surface bound to spring.datasource.hikari.* (env-overridable pool-name / maximum-pool-size / minimum-idle / idle-timeout / max-lifetime / connection-timeout / leak-detection-threshold) â€” defaults sized for the documented Prod (single tenant) deployment. ReplicaDataSourceProperties (@ConfigurationProperties on app.datasource.replica.*) with fail-fast validation; ReadWriteRoutingDataSource extends AbstractRoutingDataSource and keys off TransactionSynchronizationManager.isCurrentTransactionReadOnly() (WRITE is the default â€” no txn, flag off, or missing replica all degrade to write). ReadReplicaDataSourceConfiguration is @ConditionalOnProperty-gated on app.datasource.replica.enabled. DataSourceConfig composes (write, optional replica) behind the routing wrapper; flag-off behaviour bit-for-bit unchanged. 11 unit tests cover routing-key derivation and replica fail-fast validation. Activation playbook + 5-business-day UAT soak procedure documented in docs/runbooks/postgres-pool-replica-sizing.md.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2333,9 +2333,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers</t>
+          <t>BAA template; PHI inventory; key rotation; access review cadence â€” for international customers. Foundation pass shipped on feat/v2.0-hipaa-posture (PR #335) â€” mirrors the SOC 2 row-37 pattern. docs/compliance/hipaa-gap.md inventories 51 control points across Â§164 Security Rule (administrative / physical / technical / organizational / docs) + Privacy Rule (minimum necessary + individual rights) â€” scorecard 19 present / 17 partial / 15 gap = 54% weighted, technical-safeguards axis at 75% (Â§164.312(a)(2)(iv) Encryption + Decryption rated partial: AES-256-GCM operational on 14 narrative columns via EncryptedStringConverter, identifier columns plaintext today). Companion machine-readable docs/compliance/hipaa-controls.csv + docs/compliance/hipaa-baa-template.md (11-section BAA draft with sub-BAA table for Railway / Splunk / Grafana / Keycloak host / email + SMS vendors) + docs/compliance/phi-inventory.md (all 18 Â§164.514(b)(2) identifier categories + clinical-record body, per-column encryption status, dataflow map). 27-item remediation backlog (10 P0 / 10 P1 / 7 P2); P0 critical path 2026-09-30 calibrated to land one month after the SOC 2 P0 deadline.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2489,9 +2489,9 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities</t>
+          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities. Foundation pass shipped on feat/v1.1-fhir-write-api: V101 partial unique index uk_patient_hospital_registration_active_mrn on (hospital_id, LOWER(mrn)) WHERE is_active = true guarantees conditional-create multi-match (412) is unreachable in practice; PatientFhirWriteService delivers PUT /Patient/{id} on the FHIR-mutable subset (address/telecom/active only â€” identity columns flow through the registration admin path) and POST /Patient with If-None-Exist following the empi-identity policy (0 matches =&gt; 404, 1 =&gt; 200 with existing, &gt;1 =&gt; 412, missing/non-MRN =&gt; 422 â€” never auto-provisions); gated behind app.fhir.write.enabled=${FHIR_WRITE_ENABLED:false} so flag-off behaviour is bit-for-bit unchanged; PatientFhirMapper.applyFhirUpdates + extractMrnIdentifier + parseMrnSearchToken added on the write direction; HmsCapabilityStatementProvider advertises Patient.conditionalCreate=true only when the flag is on; 6 IT cases across PatientFhirWriteIT (flag-off â€” PUT/POST 405 + metadata omits conditionalCreate) and PatientFhirWriteEnabledIT (flag-on â€” metadata advertises, POST without If-None-Exist 422, unmatched MRN 404). Runbook: docs/runbooks/fhir-write-api.md. Encounter and Observation write paths deferred to the row-20 follow-on (Observation's 1:N PatientVitalSign expansion needs a labresult-only carve-out).</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1553,9 +1553,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox</t>
+          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox. Foundation pass shipped on feat/v1.1-cds-hooks-public-discovery: SecurityConfig.corsConfigurationSource adds an explicit sandbox-origin group gated by app.cors.cds-hooks-sandbox.enabled=true with sensible defaults (fhir.epic.com / *.epic.com / fhir-ehr-code.cerner.com / sandbox.cerner.com / *.cerner.com / launcher.smarthealthit.org / *.smarthealthit.org) so the partner sandbox UIs can probe HMS without wildcarding; PatientViewCdsService and BpaProtocolsCdsService declare prefetch templates for the FHIR queries each service consumes (patient + allergies + problems on hms-patient-view; patient + vitals + problems + medications on hms-bpa-protocols); CdsHooksDiscoveryIT replaces the single-case shape check with 5 spec-grounded assertions including a CORS preflight from https://launcher.smarthealthit.org. Runbook: docs/runbooks/cds-hooks-sandbox-validation.md. Row stays started until clean discovery+invocation pairs are recorded against all three external sandboxes (SMART App Launcher, Cerner, Epic).</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1917,9 +1917,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module</t>
+          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module. Foundation pass shipped on feat/v1.1-kpi-dashboard-service: KpiDashboardService + Impl computes the three KPIs on-demand via native SQL against clinical.encounters (arrival -&gt; triage), clinical.dispenses JOIN clinical.prescriptions (rx.created_at -&gt; dispensed_at), clinical.appointments (NO_SHOW / total) â€” tenant scope from HospitalContextHolder.getActiveHospitalId() with super-admin-without-pin returning an empty rollup; new GET /api/kpi/dashboard?from&amp;to controller with 180-day window cap + @PreAuthorize on SUPER_ADMIN/HOSPITAL_ADMIN/DOCTOR/NURSE/STAFF; hospital-portal new &lt;app-kpi-cards&gt; sub-component embedded inside analytics/ rendering 3 cards (Door-to-doctor / Dispense lead time / No-show rate) with ANALYTICS.KPI.* keys across en/fr/es; KpiDashboardControllerIT (2 cases â€” 401 + non-POST routability). Runbook: docs/runbooks/kpi-dashboard.md. Materialized-view backing deferred to the follow-on once production query load is known (H2 doesn't support MV, and premature materialization wastes autovacuum cycles); median P50 door-to-doctor, sparkline trend, and E2E axe-smoke against seeded data also follow-on.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -2177,9 +2177,9 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min</t>
+          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min. Foundation pass shipped on feat/v2.0-synthetic-monitoring: Blackbox-exporter v0.25.0 added to docker-compose under the existing observability profile; grafana/blackbox.yml ships four probe modules (http_health_2xx, http_smart_2xx, http_fhir_metadata_2xx, http_cds_discovery_2xx) with TLS verification on by default; grafana/prometheus.yml adds four scrape jobs against /actuator/health/liveness, /actuator/health/readiness, /fhir/metadata, /.well-known/smart-configuration, /cds-services with the standard relabel idiom (instance carries the human-readable target URL) and external labels application=hms, service=synthetic, geo=local; grafana/rules/alerts.yml new hms.synthetic group with three rules â€” HmsSyntheticProbeFailureRate (&gt;10% failure for 5m â€” the deliverable target, severity=page), HmsSyntheticProbeAllGeosFailing (every vantage point at 0 for 2m), HmsSyntheticProbeLatencyHigh (probe_duration_seconds &gt; 5 for 10m). Runbook: docs/runbooks/synthetic-monitoring.md. Multi-geo rollout is operational and explicitly deferred â€” pick Option A (3 Blackbox cloud regions with per-region external_labels.geo) or Option B (k6 cloud canary from amazon:us:ashburn + amazon:eu:dublin + amazon:af:cape-town) before flipping to completed.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2749,9 +2749,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities. Foundation pass shipped on feat/v1.1-fhir-write-api: V101 partial unique index uk_patient_hospital_registration_active_mrn on (hospital_id, LOWER(mrn)) WHERE is_active = true guarantees conditional-create multi-match (412) is unreachable in practice; PatientFhirWriteService delivers PUT /Patient/{id} on the FHIR-mutable subset (address/telecom/active only â€” identity columns flow through the registration admin path) and POST /Patient with If-None-Exist following the empi-identity policy (0 matches =&gt; 404, 1 =&gt; 200 with existing, &gt;1 =&gt; 412, missing/non-MRN =&gt; 422 â€” never auto-provisions); gated behind app.fhir.write.enabled=${FHIR_WRITE_ENABLED:false} so flag-off behaviour is bit-for-bit unchanged; PatientFhirMapper.applyFhirUpdates + extractMrnIdentifier + parseMrnSearchToken added on the write direction; HmsCapabilityStatementProvider advertises Patient.conditionalCreate=true only when the flag is on; 6 IT cases across PatientFhirWriteIT (flag-off â€” PUT/POST 405 + metadata omits conditionalCreate) and PatientFhirWriteEnabledIT (flag-on â€” metadata advertises, POST without If-None-Exist 422, unmatched MRN 404). Runbook: docs/runbooks/fhir-write-api.md. Encounter and Observation write paths deferred to the row-20 follow-on (Observation's 1:N PatientVitalSign expansion needs a labresult-only carve-out).</t>
+          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities. Foundation pass shipped on feat/v1.1-fhir-write-api (PR #343, merge 3f2b0c3d): V101 partial unique index uk_patient_hospital_registration_active_mrn on (hospital_id, LOWER(mrn)) WHERE is_active = true guarantees conditional-create multi-match (412) is unreachable in practice; PatientFhirWriteService delivers PUT /Patient/{id} on the FHIR-mutable subset (address/telecom/active only â€” identity columns flow through the registration admin path) and POST /Patient with If-None-Exist following the empi-identity policy (0 matches =&gt; 404, 1 =&gt; 200 with existing, &gt;1 =&gt; 412, missing/non-MRN =&gt; 422 â€” never auto-provisions); gated behind app.fhir.write.enabled=${FHIR_WRITE_ENABLED:false} so flag-off behaviour is bit-for-bit unchanged; PatientFhirMapper.applyFhirUpdates + extractMrnIdentifier + parseMrnSearchToken added on the write direction; HmsCapabilityStatementProvider advertises Patient.conditionalCreate=true only when the flag is on; 6 IT cases across PatientFhirWriteIT (flag-off â€” PUT/POST 405 + metadata omits conditionalCreate) and PatientFhirWriteEnabledIT (flag-on â€” metadata advertises, POST without If-None-Exist 422, unmatched MRN 404). Runbook: docs/runbooks/fhir-write-api.md. Encounter and Observation write paths deferred to the row-20 follow-on (Observation's 1:N PatientVitalSign expansion needs a labresult-only carve-out).</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox. Foundation pass shipped on feat/v1.1-cds-hooks-public-discovery: SecurityConfig.corsConfigurationSource adds an explicit sandbox-origin group gated by app.cors.cds-hooks-sandbox.enabled=true with sensible defaults (fhir.epic.com / *.epic.com / fhir-ehr-code.cerner.com / sandbox.cerner.com / *.cerner.com / launcher.smarthealthit.org / *.smarthealthit.org) so the partner sandbox UIs can probe HMS without wildcarding; PatientViewCdsService and BpaProtocolsCdsService declare prefetch templates for the FHIR queries each service consumes (patient + allergies + problems on hms-patient-view; patient + vitals + problems + medications on hms-bpa-protocols); CdsHooksDiscoveryIT replaces the single-case shape check with 5 spec-grounded assertions including a CORS preflight from https://launcher.smarthealthit.org. Runbook: docs/runbooks/cds-hooks-sandbox-validation.md. Row stays started until clean discovery+invocation pairs are recorded against all three external sandboxes (SMART App Launcher, Cerner, Epic).</t>
+          <t>/api/cds-services validated against Cerner and Epic CDS Hooks sandbox. Foundation pass shipped on feat/v1.1-cds-hooks-public-discovery (PR #338, merge 1a5cca78): SecurityConfig.corsConfigurationSource adds an explicit sandbox-origin group gated by app.cors.cds-hooks-sandbox.enabled=true with sensible defaults (fhir.epic.com / *.epic.com / fhir-ehr-code.cerner.com / sandbox.cerner.com / *.cerner.com / launcher.smarthealthit.org / *.smarthealthit.org) so the partner sandbox UIs can probe HMS without wildcarding; PatientViewCdsService and BpaProtocolsCdsService declare prefetch templates for the FHIR queries each service consumes (patient + allergies + problems on hms-patient-view; patient + vitals + problems + medications on hms-bpa-protocols); CdsHooksDiscoveryIT replaces the single-case shape check with 5 spec-grounded assertions including a CORS preflight from https://launcher.smarthealthit.org. Runbook: docs/runbooks/cds-hooks-sandbox-validation.md. Row stays started until clean discovery+invocation pairs are recorded against all three external sandboxes (SMART App Launcher, Cerner, Epic).</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module. Foundation pass shipped on feat/v1.1-kpi-dashboard-service: KpiDashboardService + Impl computes the three KPIs on-demand via native SQL against clinical.encounters (arrival -&gt; triage), clinical.dispenses JOIN clinical.prescriptions (rx.created_at -&gt; dispensed_at), clinical.appointments (NO_SHOW / total) â€” tenant scope from HospitalContextHolder.getActiveHospitalId() with super-admin-without-pin returning an empty rollup; new GET /api/kpi/dashboard?from&amp;to controller with 180-day window cap + @PreAuthorize on SUPER_ADMIN/HOSPITAL_ADMIN/DOCTOR/NURSE/STAFF; hospital-portal new &lt;app-kpi-cards&gt; sub-component embedded inside analytics/ rendering 3 cards (Door-to-doctor / Dispense lead time / No-show rate) with ANALYTICS.KPI.* keys across en/fr/es; KpiDashboardControllerIT (2 cases â€” 401 + non-POST routability). Runbook: docs/runbooks/kpi-dashboard.md. Materialized-view backing deferred to the follow-on once production query load is known (H2 doesn't support MV, and premature materialization wastes autovacuum cycles); median P50 door-to-doctor, sparkline trend, and E2E axe-smoke against seeded data also follow-on.</t>
+          <t>Materialized views for avg door-to-doctor, dispense lead time, no-show rate; surfaced in existing analytics/ module. Foundation pass shipped on feat/v1.1-kpi-dashboard-service (PR #341, merge 74abb291): KpiDashboardService + Impl computes the three KPIs on-demand via native SQL against clinical.encounters (arrival -&gt; triage), clinical.dispenses JOIN clinical.prescriptions (rx.created_at -&gt; dispensed_at), clinical.appointments (NO_SHOW / total) â€” tenant scope from HospitalContextHolder.getActiveHospitalId() with super-admin-without-pin returning an empty rollup; new GET /api/kpi/dashboard?from&amp;to controller with 180-day window cap + @PreAuthorize on SUPER_ADMIN/HOSPITAL_ADMIN/DOCTOR/NURSE/STAFF; hospital-portal new &lt;app-kpi-cards&gt; sub-component embedded inside analytics/ rendering 3 cards (Door-to-doctor / Dispense lead time / No-show rate) with ANALYTICS.KPI.* keys across en/fr/es; KpiDashboardControllerIT (2 cases â€” 401 + non-POST routability). Runbook: docs/runbooks/kpi-dashboard.md. Materialized-view backing deferred to the follow-on once production query load is known (H2 doesn't support MV, and premature materialization wastes autovacuum cycles); median P50 door-to-doctor, sparkline trend, and E2E axe-smoke against seeded data also follow-on.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min. Foundation pass shipped on feat/v2.0-synthetic-monitoring: Blackbox-exporter v0.25.0 added to docker-compose under the existing observability profile; grafana/blackbox.yml ships four probe modules (http_health_2xx, http_smart_2xx, http_fhir_metadata_2xx, http_cds_discovery_2xx) with TLS verification on by default; grafana/prometheus.yml adds four scrape jobs against /actuator/health/liveness, /actuator/health/readiness, /fhir/metadata, /.well-known/smart-configuration, /cds-services with the standard relabel idiom (instance carries the human-readable target URL) and external labels application=hms, service=synthetic, geo=local; grafana/rules/alerts.yml new hms.synthetic group with three rules â€” HmsSyntheticProbeFailureRate (&gt;10% failure for 5m â€” the deliverable target, severity=page), HmsSyntheticProbeAllGeosFailing (every vantage point at 0 for 2m), HmsSyntheticProbeLatencyHigh (probe_duration_seconds &gt; 5 for 10m). Runbook: docs/runbooks/synthetic-monitoring.md. Multi-geo rollout is operational and explicitly deferred â€” pick Option A (3 Blackbox cloud regions with per-region external_labels.geo) or Option B (k6 cloud canary from amazon:us:ashburn + amazon:eu:dublin + amazon:af:cape-town) before flipping to completed.</t>
+          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min. Foundation pass shipped on feat/v2.0-synthetic-monitoring (PR #342, merge 638e8d72): Blackbox-exporter v0.25.0 added to docker-compose under the existing observability profile; grafana/blackbox.yml ships four probe modules (http_health_2xx, http_smart_2xx, http_fhir_metadata_2xx, http_cds_discovery_2xx) with TLS verification on by default; grafana/prometheus.yml adds four scrape jobs against /actuator/health/liveness, /actuator/health/readiness, /fhir/metadata, /.well-known/smart-configuration, /cds-services with the standard relabel idiom (instance carries the human-readable target URL) and external labels application=hms, service=synthetic, geo=local; grafana/rules/alerts.yml new hms.synthetic group with three rules â€” HmsSyntheticProbeFailureRate (&gt;10% failure for 5m â€” the deliverable target, severity=page), HmsSyntheticProbeAllGeosFailing (every vantage point at 0 for 2m), HmsSyntheticProbeLatencyHigh (probe_duration_seconds &gt; 5 for 10m). Runbook: docs/runbooks/synthetic-monitoring.md. Multi-geo rollout is operational and explicitly deferred â€” pick Option A (3 Blackbox cloud regions with per-region external_labels.geo) or Option B (k6 cloud canary from amazon:us:ashburn + amazon:eu:dublin + amazon:af:cape-town) before flipping to completed.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities. Foundation pass shipped on feat/v1.1-fhir-write-api: V101 partial unique index uk_patient_hospital_registration_active_mrn on (hospital_id, LOWER(mrn)) WHERE is_active = true guarantees conditional-create multi-match (412) is unreachable in practice; PatientFhirWriteService delivers PUT /Patient/{id} on the FHIR-mutable subset (address/telecom/active only â€” identity columns flow through the registration admin path) and POST /Patient with If-None-Exist following the empi-identity policy (0 matches =&gt; 404, 1 =&gt; 200 with existing, &gt;1 =&gt; 412, missing/non-MRN =&gt; 422 â€” never auto-provisions); gated behind app.fhir.write.enabled=${FHIR_WRITE_ENABLED:false} so flag-off behaviour is bit-for-bit unchanged; PatientFhirMapper.applyFhirUpdates + extractMrnIdentifier + parseMrnSearchToken added on the write direction; HmsCapabilityStatementProvider advertises Patient.conditionalCreate=true only when the flag is on; 6 IT cases across PatientFhirWriteIT (flag-off â€” PUT/POST 405 + metadata omits conditionalCreate) and PatientFhirWriteEnabledIT (flag-on â€” metadata advertises, POST without If-None-Exist 422, unmatched MRN 404). Runbook: docs/runbooks/fhir-write-api.md. Encounter and Observation write paths deferred to the row-20 follow-on (Observation's 1:N PatientVitalSign expansion needs a labresult-only carve-out).</t>
+          <t>POST/PUT for Patient, Encounter, Observation; conditional create via If-None-Exist; metadata updated to advertise write capabilities. Foundation pass shipped on feat/v1.1-fhir-write-api: V101 partial unique index uk_patient_hospital_registration_active_mrn on (hospital_id, LOWER(mrn)) WHERE is_active = true guarantees conditional-create multi-match (412) is unreachable in practice; PatientFhirWriteService delivers PUT /Patient/{id} on the FHIR-mutable subset (address/telecom/active only â€” identity columns flow through the registration admin path) and POST /Patient with If-None-Exist following the empi-identity policy (0 matches =&gt; 404, 1 =&gt; 200 with existing, &gt;1 =&gt; 412, missing/non-MRN =&gt; 422 â€” never auto-provisions); gated behind app.fhir.write.enabled=${FHIR_WRITE_ENABLED:false} so flag-off behaviour is bit-for-bit unchanged; PatientFhirMapper.applyFhirUpdates + extractMrnIdentifier + parseMrnSearchToken added on the write direction; HmsCapabilityStatementProvider advertises Patient.conditionalCreate=true only when the flag is on; 6 IT cases across PatientFhirWriteIT (flag-off â€” PUT/POST 405 + metadata omits conditionalCreate) and PatientFhirWriteEnabledIT (flag-on â€” metadata advertises, POST without If-None-Exist 422, unmatched MRN 404). Row-20 follow-on shipped on feat/v1.1-fhir-write-encounter-observation: EncounterFhirWriteService delivers PUT /Encounter/{id} on a very narrow subset (period.end -&gt; checkoutTimestamp only when currently null; reasonCode[0].text -&gt; chiefComplaint only when currently null/blank); tenant scope via EncounterRepository.findByIdAndHospital_Id + defence-in-depth hospital match on the loaded entity (missing scope or mismatch -&gt; 403); new AuditEventType.ENCOUNTER_UPDATE with entityType=ENCOUNTER. ObservationFhirWriteService delivers PUT /Observation/labresult-{uuid} honoring only note[0].text (appended with pipe-separator if notes already non-blank; duplicate text is a no-op); PUT /Observation/vital-* is rejected 422 BUSINESSRULE (1:N source-row expansion has no single write target â€” labresult-only carve-out from the foundation cell); LAB_RESULT_UPDATED audit with entityType=LAB_RESULT. HmsCapabilityStatementProvider extended to advertise/strip update interaction on Encounter + Observation in step with the flag. PR #343 Copilot-flagged flag-first ordering applied uniformly on PatientFhirResourceProvider @Update + @Create (the original gap noted in fhir-r4-api skill) and on the new Encounter + Observation @Update handlers. Runbook docs/runbooks/fhir-write-api.md extended with the Encounter + Observation honored-subset tables + tenant gate + audit emission. 8 new ITs (EncounterFhirWriteIT/EnabledIT: 2 + 1; ObservationFhirWriteIT/EnabledIT: 3 + 2 â€” flag-off rejection + flag-on metadata + flag-on vital-* labresult-only carve-out). POST /Encounter and POST /Observation explicitly deferred indefinitely (in-app workflow remains canonical creation path); row stays started until SMART App Launcher + Cerner + Epic sandbox conformance soak is recorded.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Bulk export for Patient and Group; output to S3-compatible bucket; documented in docs/fhir-bulk.md</t>
+          <t>Bulk export for Patient and Group; output to S3-compatible bucket; documented in docs/fhir-bulk.md. Foundation pass shipped on feat/v1.1-fhir-bulk-and-everything: FhirOperationsProperties gates the operation under app.fhir.operations.bulk-export.enabled (default false). FhirBulkExportOperationProvider exposes POST /api/fhir/$export (system) + POST /api/fhir/Patient/$export (type-level) as HAPI plain-provider @Operation methods with manualResponse=true; each accepted call returns 202 + Content-Location pointing at /api/fhir-bulk-status/{jobId} (sibling Spring controller because HAPI captures /api/fhir/*; canonical $export-poll-status mounting deferred with the runner). FhirBulkExportService holds an in-memory ConcurrentHashMap of BulkExportJobState; tenant scope from HospitalContextHolder.getActiveHospitalId() pinned at creation, status/cancel from another tenant collapse to 404 (no information leak); honors _since (ISO-8601) and _type (CSV). FhirBulkExportStatusController returns 202+Retry-After:120 on GET (always in-progress in foundation pass) and 202 on DELETE drop, 404 on miss or cross-tenant. HmsCapabilityStatementProvider's new applyOperationVisibility strips the export operation entry when the flag is off so /metadata matches runtime behaviour. AuditEventType.DATA_EXPORT emitted with entityType=FHIR_BULK_EXPORT_JOB on kickoff + cancel. 4 ITs across FhirBulkExportIT (flag-off â€” kickoff system + Patient + status + metadata-omit) and FhirBulkExportEnabledIT (flag-on â€” metadata advertises). Group-level $export deferred (needs GroupFhirResourceProvider); the async NDJSON runner (S3 streaming + persistent fhir_bulk_export_jobs table + output manifest 200 response + spec-compliant 501 on flag-off) is the named row-21 follow-on. Runbook: docs/fhir-bulk.md.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1605,9 +1605,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Patient compartment export; required by most HIE handshakes</t>
+          <t>Patient compartment export; required by most HIE handshakes. Foundation pass shipped on feat/v1.1-fhir-bulk-and-everything: app.fhir.operations.everything.enabled (default false). @Operation(name="$everything", type=Patient.class) on PatientFhirResourceProvider delegates to PatientEverythingService.everythingForPatient(uuid). The service assembles a Bundle (type=searchset) of 1 Patient + up to 200 Encounters (hospital-scoped) + up to 200 vital-sign rows (each fan-out 1:N into Observation resources by ObservationFhirMapper) + up to 200 lab-result Observations (hospital-scoped via labOrder.hospital) + all Conditions (problem list) + up to 200 MedicationRequests (hospital-scoped). Tenant scope: missing active hospital -&gt; 403 Forbidden; cross-tenant patient -&gt; 404. AuditEventType.PATIENT_EXPORT emitted with entry-count description. HmsCapabilityStatementProvider strips the everything operation entry when the flag is off. 2 ITs: PatientEverythingIT (flag-off â€” 401/405 + metadata omit) and PatientEverythingEnabledIT (flag-on â€” metadata advertises). Authenticated wire-level Bundle composition assertion + _since / _type / page cursor / start-end date params + SMART App Launcher conformance soak are the named row-22 follow-on.</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1657,9 +1657,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -57,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -911,7 +911,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Flip OIDC_REQUIRED=true in UAT; soak 7 days; promote to prod; legacy /auth/login returns 410 Gone</t>
+          <t>Flip OIDC_REQUIRED=true in UAT; soak 7 days; promote to prod; legacy /auth/login returns 410 Gone. Foundation pass shipped on chore/v1.0-keycloak-cutover-and-cost-obs: docs/runbooks/keycloak-cutover-sequence.md chains rows 18 -&gt; 19 -&gt; 8(uat, 7-day soak) -&gt; 8(prod, 48 h smoke) with hard go/no-go gates between each step and a rollback decision tree. scripts/keycloak/preflight.sh wraps the precondition checklists from keycloak-migration-runbook.md + keycloak-cutover-runbook.md into one harness (R1-R4 + P1-P4 via env-sync-verify.sh --public-only; OIDC discovery + issuer match; optional A1-A3 when admin token is set; optional backend health when HMS_BACKEND_BASE_URL is set). Row stays started until the prod cutover smoke is green for 48 h and the postmortem doc lands.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak â‰¥ 5 business days before promoting to prod.</t>
+          <t>Apply hosted-dev playbook to uat: dedicated migration-admin in master realm, hms_read read-only role on hms-Postgres-uat with SELECT grants on security.users + security.user_role_hospital_assignment + security.roles, SMTP configured on uat hms realm, dry-run + live run + execute-actions-email re-trigger, partial-import clients from realm-export.json. Soak â‰¥ 5 business days before promoting to prod. Foundation pass shipped on chore/v1.0-keycloak-cutover-and-cost-obs: the uat migration is now step 1 of the conductor playbook docs/runbooks/keycloak-cutover-sequence.md (existing keycloak-migration-runbook.md remains the per-step procedure). scripts/keycloak/preflight.sh verifies every precondition (realm-export drift, redirect-URI coverage, frontend env-file agreement, OIDC discovery match) before the live run kicks off â€” exits non-zero on the first failure. Row stays started until the live run is executed against hms-keycloak-uat and the 5-business-day soak completes clean.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Apply same playbook to hms-keycloak-prod during announced maintenance window per docs/runbooks/keycloak-cutover-runbook.md. Prereq: uat soak clean. Pairs with the existing 'Keycloak Phase C cutover' row (which covers the OIDC_REQUIRED=true flip that gates legacy auth).</t>
+          <t>Apply same playbook to hms-keycloak-prod during announced maintenance window per docs/runbooks/keycloak-cutover-runbook.md. Prereq: uat soak clean. Pairs with the existing 'Keycloak Phase C cutover' row (which covers the OIDC_REQUIRED=true flip that gates legacy auth). Foundation pass shipped on chore/v1.0-keycloak-cutover-and-cost-obs: prod migration is step 2 of docs/runbooks/keycloak-cutover-sequence.md with prod-specific gates â€” pre-run pg_dump of the Keycloak DB (rollback dependency), never on a Friday, on-call rotation with rollback authority, 24-hour observation against prod migration metrics before stepping to row-8 flip. Row stays started until the live run executes against hms-keycloak-prod and 24-hour observation closes clean.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -1605,7 +1605,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1657,7 +1657,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1709,7 +1709,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -1761,7 +1761,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -1813,7 +1813,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -1865,7 +1865,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -1917,7 +1917,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -1969,7 +1969,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2073,7 +2073,7 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2125,7 +2125,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2177,7 +2177,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2229,7 +2229,7 @@
           <t>Mixed (Backend + Platform)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2281,7 +2281,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2333,7 +2333,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2385,7 +2385,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2437,7 +2437,7 @@
           <t>Mixed (Compliance + Backend)</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2489,7 +2489,7 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2541,7 +2541,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2593,7 +2593,7 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2645,7 +2645,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2697,7 +2697,7 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>not-started</t>
         </is>
@@ -2749,7 +2749,7 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>started</t>
         </is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Tag every Splunk event + Grafana series with tenant; chargeback report per hospital</t>
+          <t>Tag every Splunk event + Grafana series with tenant; chargeback report per hospital. Foundation pass shipped on chore/v1.0-keycloak-cutover-and-cost-obs: TenantCostObservabilityProperties under app.observability.tenant-cost.enabled (default false). ChargebackReportService aggregates per-hospital audit-event counts over a date window via new AuditEventLogRepository.countByHospitalBetween JPQL (groups by the denormalized AuditEventLog.hospital_name; rows without snapshot excluded â€” those belong to a future platform-shared bucket). ChargebackReportController exposes GET /api/super-admin/cost/per-tenant?from&amp;to (SUPER_ADMIN only; default trailing-30-day window; 92-day cap; flag-off returns 404 so the endpoint shape stays hidden). Tenant labeling on Splunk is already in place via the existing AuditEventLog.hospital_name snapshot + the SplunkHecAppender's structured-JSON write â€” no code change needed; Grafana per-tenant tagging is deferred (needs a Micrometer MeterFilter that reads HospitalContextHolder at sample time). 5 new tests: ChargebackReportServiceTest (4 cases: flag passthrough + maps Object[] rows + accepts Integer count + empty-list passthrough) and ChargebackReportControllerIT (1 case: flag-off 401/404 split). Splunk event-count + Grafana series-cardinality + Postgres storage-bytes inputs + per-deployment currency cost model + Control Tower panel are the named row-44 follow-on. Runbook: docs/runbooks/per-tenant-cost-observability.md.</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>not-started</t>
+          <t>started</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set. Foundation pass shipped on feat/v2.0-foundation-batch: EmpiProbabilisticProperties under app.empi.probabilistic.enabled (default false, min-score=0.7, max-candidates=10). EmpiProbabilisticMatcher.findCandidates(query) returns empty list both flag-off AND flag-on (scorer body deliberately deferred â€” see runbook). EmpiCandidateQueryDTO (firstName/lastName/dateOfBirth/sex/nationalId) + EmpiCandidateMatchDTO (patientId/displayName/score + per-field confidence booleans). EmpiProbabilisticController POST /api/empi/candidates with @PreAuthorize(SUPER_ADMIN/HOSPITAL_ADMIN/RECEPTIONIST/NURSE/DOCTOR); flag-off returns 404. 5 new tests: EmpiProbabilisticMatcherTest (4 unit cases pinning the empty-contract) + EmpiProbabilisticControllerIT (1 IT â€” flag-off 401/404). The Fellegi-Sunter scorer body + labelled audit set + ROC analysis + receptionist UI are the named row-25 follow-on â€” deferred deliberately so threshold tuning happens against real labelled data, not against intuition. Runbook: docs/runbooks/empi-probabilistic-matching.md.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1813,9 +1813,9 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking</t>
+          <t>Move ORU result + dispense settlement to Kafka consumers; reduce request-thread blocking. Foundation pass shipped on feat/v2.0-foundation-batch: AsyncPipelineProperties under app.async.pipeline.enabled (default false) with env-configurable oruResultTopic / dispenseSettlementTopic / consumerGroup names. No @KafkaListener bodies and no producer-side branches ship â€” the consumer + producer wiring is the named row-36 follow-on, deferred until row 23 (ORU^R01 -&gt; LabResult persistence) has soaked 14 days against real Mindray/Sysmex traffic so the synchronous path's latency baseline is established and the analyzer-retransmit semantics aren't entangled with Kafka-consumer-retry semantics in the eventual incident triage. Runbook: docs/runbooks/async-kafka-pipeline.md.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2385,9 +2385,9 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales</t>
+          <t>Per-tenant region pinning (Railway â†’ AWS or OVH-Africa); required for Senegal/CÃ´te d'Ivoire/Ghana sales. Foundation pass shipped on feat/v2.0-foundation-batch: decision-record doc docs/compliance/ecowas-residency-decision-record.md capturing the per-country residency requirements (Senegal CDP, CI ARTCI, Ghana DPC, BF CIL, Nigeria NDPR, plus framework for the others) + the two viable cloud-procurement options (AWS af-south-1 managed services vs OVH Dakar bare-metal in-country) + the decision criteria matrix (strict residency, ops surface, latency, multi-country expansion, IaC compatibility, row-21 S3 compatibility). No code or schema changes â€” the existing V82 Organization.region column stays as the data-plane the eventual routing layer keys off. The decision blocker is owned by Sales (which ECOWAS customer signs first + what their counsel demands), not Engineering. The row-39 follow-on (region_pin column on hospital.organizations + RegionRoutingService + per-tenant migration playbook + ORGANIZATION_REGION_UPDATED audit extension) ships only after the cloud-vendor decision lands.</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2541,9 +2541,9 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI</t>
+          <t>Complete the partially-designed HighRiskPregnancyCarePlan*, NewbornAssessment*, PostpartumCare* services and matching UI. Foundation pass shipped on feat/v2.0-foundation-batch: scope-audit doc docs/runbooks/obgyn-pediatrics-finish-scope-audit.md establishing that the three services already exist as substantial implementations (~391 + ~422 + ~676 LOC respectively) â€” the deliverable's 'finish' language is misleading; what's actually missing is (1) cross-service workflow integration (Pregnancy.outcome enum + NewbornAssessment.parentPregnancyId FK + PostpartumCare.newbornAssessmentId FK + PostpartumCareâ†’ImmunizationService auto-enqueue), (2) three new clinical surfaces (antepartum/partogram, postpartum-hemorrhage emergency, pediatric EPI schedule projector), (3) three frontend completion gaps (visit-schedule panel + feeding-plan/screening/discharge-readiness + contraception-counselling/immunization-embed), (4) PHI encryption audit on NewbornAssessment columns, (5) cross-service happy-path IT. No service code changes today â€” each gap is sized for its own foundation-pass PR rather than one huge bundle. Row stays started until all nine follow-on items close.</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2645,9 +2645,9 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing</t>
+          <t>Extend existing imaging/ module with Orthanc or dcm4chee adapter for actual image viewing. Foundation pass shipped on feat/v2.0-foundation-batch: DicomProxyProperties under app.imaging.dicom-proxy.enabled (default false) with adapter=orthanc|dcm4chee + env-configurable baseUrl. DicomProxyService.listInstancesForStudy(studyUid) emits AuditEventType.IMAGING_RESULT_UPDATED with entityType=IMAGING_STUDY on every flag-on call so the trail accumulates real-world usage data; the upstream HTTP call is the named row-42 follow-on. DicomProxyController GET /api/imaging/dicom/{studyUid}/instances with @PreAuthorize(SUPER_ADMIN/HOSPITAL_ADMIN/DOCTOR/NURSE/RADIOLOGIST); flag-off returns 404. 5 new tests: DicomProxyServiceTest (4 unit cases â€” flag passthrough + audit gating + blank-UID guard) + DicomProxyControllerIT (1 IT â€” flag-off 401/404). Why proxy instead of direct PACS link: closes the audit/auth/tenant-isolation gaps in the existing V75 pacs_viewer_url_template path. Follow-on: OrthancDicomProxyAdapter + Dcm4cheeDicomProxyAdapter via DICOMweb QIDO-RS + WADO-RS streaming + cross-tenant gate + per-hospital PACS routing + Redis cache + &lt;app-dicom-viewer&gt; Angular component. Runbook: docs/runbooks/dicom-proxy.md.</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2697,9 +2697,9 @@
           <t>Mixed (Backend + Frontend)</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>started</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set. Foundation pass shipped on feat/v2.0-foundation-batch: EmpiProbabilisticProperties under app.empi.probabilistic.enabled (default false, min-score=0.7, max-candidates=10). EmpiProbabilisticMatcher.findCandidates(query) returns empty list both flag-off AND flag-on (scorer body deliberately deferred â€” see runbook). EmpiCandidateQueryDTO (firstName/lastName/dateOfBirth/sex/nationalId) + EmpiCandidateMatchDTO (patientId/displayName/score + per-field confidence booleans). EmpiProbabilisticController POST /api/empi/candidates with @PreAuthorize(SUPER_ADMIN/HOSPITAL_ADMIN/RECEPTIONIST/NURSE/DOCTOR); flag-off returns 404. 5 new tests: EmpiProbabilisticMatcherTest (4 unit cases pinning the empty-contract) + EmpiProbabilisticControllerIT (1 IT â€” flag-off 401/404). The Fellegi-Sunter scorer body + labelled audit set + ROC analysis + receptionist UI are the named row-25 follow-on â€” deferred deliberately so threshold tuning happens against real labelled data, not against intuition. Runbook: docs/runbooks/empi-probabilistic-matching.md.</t>
+          <t>Probabilistic match on name + DOB + sex + national-ID where present; candidate-match workflow in receptionist UI; â‰¥90% recall on labelled audit set. Foundation pass shipped on feat/v2.0-foundation-batch: EmpiProbabilisticProperties under app.empi.probabilistic.enabled (default false, min-score=0.7, max-candidates=10). EmpiProbabilisticMatcher.findCandidates(query) returns empty list both flag-off AND flag-on (scorer body deliberately deferred â€” see runbook). EmpiCandidateQueryDTO (firstName/lastName/dateOfBirth/sex/nationalId) + EmpiCandidateMatchDTO (patientId/displayName/score + per-field confidence booleans). EmpiProbabilisticController POST /api/empi/candidates with @PreAuthorize(SUPER_ADMIN/HOSPITAL_ADMIN/RECEPTIONIST/NURSE/DOCTOR); flag-off returns 404. 5 new tests: EmpiProbabilisticMatcherTest (4 unit cases pinning the empty-contract) + EmpiProbabilisticControllerIT (1 IT â€” flag-off 401/403/404). The Fellegi-Sunter scorer body + labelled audit set + ROC analysis + receptionist UI are the named row-25 follow-on â€” deferred deliberately so threshold tuning happens against real labelled data, not against intuition. Runbook: docs/runbooks/empi-probabilistic-matching.md.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1929,14 +1929,14 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>v1.1</t>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability</t>
+          <t>Add Referrals, Treatments, Billing screens to Android app to match web portal capability. Deferred 2026-05-17 â€” mobile-team domain; no v1.1 driver yet. Pick up once a mobile contributor lands; cluster with rows 29/30/31 (shared team + tooling).</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1969,26 +1969,26 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>#h2.exit</t>
+          <t>#h3.exit</t>
         </is>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>v1.1</t>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability</t>
+          <t>Add Referrals, Treatments, Billing screens to iOS app to match web portal capability. Deferred 2026-05-17 â€” same as row 28 (mobile-team domain; no v1.1 driver yet).</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2021,26 +2021,26 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>#h2.exit</t>
+          <t>#h3.exit</t>
         </is>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>v1.1</t>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail</t>
+          <t>FCM/APNs already wired backend-side; add UI toggles + deep links to LabResultsDetail. Deferred 2026-05-17 â€” blocked on rows 28/29 mobile parity; backend wiring stays as-is.</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -2073,26 +2073,26 @@
           <t>Mixed (Mobile + Backend)</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>#h2.exit</t>
+          <t>#h3.exit</t>
         </is>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>v1.1</t>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E</t>
+          <t>Bring per-app test count from 5 to 30+ (unit + UI snapshots); add Detox or Maestro for E2E. Deferred 2026-05-17 â€” same mobile-team domain as row 28; bundles with the mobile parity cluster.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2125,14 +2125,14 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>#h2.exit</t>
+          <t>#h3.exit</t>
         </is>
       </c>
     </row>
@@ -2241,14 +2241,14 @@
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>v2.0</t>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>oos</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index</t>
+          <t>One-command provision: realm, schema, seed data, observability namespace, Splunk index. Deferred 2026-05-17 â€” depends on row 33 (schema-per-tenant) being substantially further along than its current foundation pass; pickable once provision-schema.sh, copy-rows.sh, and the cache-invalidation endpoint land.</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -2281,14 +2281,14 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>#h3.exit</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>
@@ -2553,14 +2553,14 @@
       </c>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>v2.0</t>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>oos</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>â€”</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent</t>
+          <t>National-ID-keyed; explicit patient Consent resource per data-sharing event; FHIR Consent. Deferred 2026-05-17 â€” depends on row 25 (EMPI v0). PR 3 unblocks the scorer follow-on but the cross-tenant + Consent surface remains substantial; revisit after EMPI v0 lands and stabilises.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2593,14 +2593,14 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>not-started</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>deferred</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>#h3.exit</t>
+          <t>â€”</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ADT^A01/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented. Foundation pass shipped on feat/v1.1-adt-admission-encounter-sync (PR #332): V99 migration adds external_visit_number + external_sending_application + external_sending_facility + external_message_control_id (nullable) to admissions and clinical.encounters with partial composite unique indexes scoped per (sender, hospital); MllpInboundAdtVisitProjectionService reconciles inbound A01/A04/A08 against existing rows by the HL7 visit-number triplet, REQUIRES_NEW so projection failure cannot roll back the demographic write; gated behind app.hl7.adt.visit-sync.enabled (default false) so flag-off behaviour is bit-for-bit unchanged. Conflict-resolution rules + operator playbook in docs/runbooks/hl7-adt-conflict-resolution.md. Auto-create deferred to a follow-on PR (needs per-hospital intake-provider config).</t>
+          <t>ADT^A01/A02/A03/A04/A08 trigger Admission and Encounter sync; conflict-resolution rules documented. Foundation pass shipped on feat/v1.1-adt-admission-encounter-sync (PR #332). A01 auto-create + A04 Encounter auto-create + per-hospital intake config (V103/V104) shipped on the follow-ons. Discharge / transfer + admin UI shipped on feat/v1.1-adt-discharge-transfer-and-intake-admin-ui: dispatcher accept-list extended to A02 + A03; MllpInboundAdtVisitProjectionService gains applyDischarge (A03 -&gt; AdmissionStatus.DISCHARGED + actualDischargeDateTime from PV1-45 falling back to now(), idempotent re-send skips audit when row is already DISCHARGED, calculateLengthOfStay refreshed) and applyTransfer (A02 -&gt; Department lookup via findByHospitalIdAndCodeIgnoreCase then findByHospitalIdAndNameIgnoreCase, unresolved destination still audits with the raw token preserved); VisitProjectionResult gains ADMISSION_DISCHARGED + ADMISSION_TRANSFERRED; new audit event types ADMISSION_DISCHARGED + ADMISSION_TRANSFERRED follow the past-tense convention. Admin REST CRUD AdtIntakeProviderConfigController POST/GET/DELETE /api/admin/adt-intake-configs gated on ROLE_SUPER_ADMIN, upsert idempotent on hospitalId. Angular admin UI at /admin/adt-intake-configs with EN+FR+ES i18n. 13 new tests (5 A02 + 4 A03 unit cases on MllpInboundAdtVisitProjectionServiceImplTest, AdtIntakeProviderConfigControllerTest 7 cases, AdtIntakeProviderConfigControllerSecurityTest reflection guard, AdtIntakeConfigComponent karma spec 5 cases). Conflict-resolution rules + operator playbook in docs/runbooks/hl7-adt-conflict-resolution.md. Row stays started until the runbook chapters for A02/A03 land + the admin form gains a hospital picker / department typeahead (currently raw-UUID inputs).</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards. Foundation pass shipped on feat/v2.0-read-replicas-hikari (PR #334): full Hikari tuning surface bound to spring.datasource.hikari.* (env-overridable pool-name / maximum-pool-size / minimum-idle / idle-timeout / max-lifetime / connection-timeout / leak-detection-threshold) â€” defaults sized for the documented Prod (single tenant) deployment. ReplicaDataSourceProperties (@ConfigurationProperties on app.datasource.replica.*) with fail-fast validation; ReadWriteRoutingDataSource extends AbstractRoutingDataSource and keys off TransactionSynchronizationManager.isCurrentTransactionReadOnly() (WRITE is the default â€” no txn, flag off, or missing replica all degrade to write). ReadReplicaDataSourceConfiguration is @ConditionalOnProperty-gated on app.datasource.replica.enabled. DataSourceConfig composes (write, optional replica) behind the routing wrapper; flag-off behaviour bit-for-bit unchanged. 11 unit tests cover routing-key derivation and replica fail-fast validation. Activation playbook + 5-business-day UAT soak procedure documented in docs/runbooks/postgres-pool-replica-sizing.md.</t>
+          <t>Hikari pool sized to actual concurrent users; RO replica routing for FHIR reads and dashboards. Foundation pass shipped on feat/v2.0-read-replicas-hikari (PR #334). Follow-on shipped on feat/v2.0-row-35-43-readreplica-healthindicator-synthetic-multigeo: ReadReplicaHealthIndicator (Component named "readReplica" + @ConditionalOnEnabledHealthIndicator("readReplica")) consolidates wiring posture (routing=enabled|disabled|missing-wrapper), READ-route probe (routedTo=READ|WRITE — surfaces lenient-fallback misroutes even when the probe itself succeeds), and per-call replica freshness (replicaInRecovery, replicaLastReplayTimestamp, replicaLagSeconds via pg_is_in_recovery() + pg_last_xact_replay_timestamp() + EXTRACT(EPOCH FROM now() - last_replay) on the replica pool directly); reports DOWN iff flag intent disagrees with the wired bean graph; opt-out per env via management.health.readReplica.enabled=false. scripts/db/replica-preflight.sh six-check operator harness (env-var presence + URL well-formedness, primary SELECT 1, replica SELECT 1, pg_is_in_recovery()=true (catches replica DSN pointing at primary — the fastest data-corruption path), lag within REPLICA_LAG_BUDGET_SECONDS=5 cross-checked against LSN equality so idle-primary doesn't false-fail, pg_read_all_data membership or SELECT on hospital.patients as the Postgres &lt; 14 fallback); exits non-zero on first failure so a CI / cutover script can gate on the exit code; POSTGRES_VERSION_OVERRIDE escape hatch documented. 5 new ReadReplicaHealthIndicatorTest cases (flag-off baseline / wiring-drift DOWN / READ happy / lenient-fallback WRITE / probe-failure DOWN). Runbook docs/runbooks/postgres-pool-replica-sizing.md updated with the new endpoint + script under Activation playbook step 3 + step 6. Row stays started until a hosted environment runs the 5-business-day UAT soak with the indicator reporting routedTo=READ across the window — actual replica provisioning is operational.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min. Foundation pass shipped on feat/v2.0-synthetic-monitoring (PR #342, merge 638e8d72): Blackbox-exporter v0.25.0 added to docker-compose under the existing observability profile; grafana/blackbox.yml ships four probe modules (http_health_2xx, http_smart_2xx, http_fhir_metadata_2xx, http_cds_discovery_2xx) with TLS verification on by default; grafana/prometheus.yml adds four scrape jobs against /actuator/health/liveness, /actuator/health/readiness, /fhir/metadata, /.well-known/smart-configuration, /cds-services with the standard relabel idiom (instance carries the human-readable target URL) and external labels application=hms, service=synthetic, geo=local; grafana/rules/alerts.yml new hms.synthetic group with three rules â€” HmsSyntheticProbeFailureRate (&gt;10% failure for 5m â€” the deliverable target, severity=page), HmsSyntheticProbeAllGeosFailing (every vantage point at 0 for 2m), HmsSyntheticProbeLatencyHigh (probe_duration_seconds &gt; 5 for 10m). Runbook: docs/runbooks/synthetic-monitoring.md. Multi-geo rollout is operational and explicitly deferred â€” pick Option A (3 Blackbox cloud regions with per-region external_labels.geo) or Option B (k6 cloud canary from amazon:us:ashburn + amazon:eu:dublin + amazon:af:cape-town) before flipping to completed.</t>
+          <t>Grafana k6 cloud or Blackbox-exporter probes from 3 geos; alert on &gt; 10% probe failure for 5 min. Foundation pass shipped on feat/v2.0-synthetic-monitoring (PR #342, merge 638e8d72). Multi-geo template follow-on shipped on feat/v2.0-row-35-43-readreplica-healthindicator-synthetic-multigeo: deployable templates for both options. Option A (grafana/prometheus-multigeo.example.yml) — per-region copy of the in-cluster Prometheus config with four placeholders (GEO_LABEL, BLACKBOX_HOST, HMS_PUBLIC_BASE_URL, MIMIR_REMOTE_WRITE_URL); remote_writes to a shared Mimir tenant so the existing HmsSyntheticProbeFailureRate / HmsSyntheticProbeAllGeosFailing alerts evaluate across geos without rule changes; load-bearing detail (external_labels.geo wins at remote_write time, do NOT also stamp via relabel_configs). Option B (scripts/perf/synthetic-canary-k6.js) — k6 cloud canary distinct from dispense-baseline.js (1 VU per zone, 5min, no auth, no PHI), distribution block targets amazon:us:ashburn + amazon:eu:dublin + amazon:af:cape-town, emits probe_success Rate + probe_duration_seconds Trend so the same alert rules fire on identical series shapes; k6 thresholds mirror the &gt;10%-failure deliverable so the cloud run itself fails on regression. Runbook docs/runbooks/synthetic-monitoring.md rewritten with concrete deployable references for both options + a Choosing-between-A-and-B trade-off matrix (cost, vendor lock-in, ECOWAS path). Row stays started until a hosted environment actually runs one of the two — actual cloud-account provisioning is operational.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
